--- a/PFE/stress_pfe_view_matrix.xlsx
+++ b/PFE/stress_pfe_view_matrix.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Join × business_date Audit" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base Tables" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Anomalies &amp; Conformance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements Tally" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'View Matrix'!$A$4:$G$11</definedName>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +85,14 @@
       <color rgb="002E7D32"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -187,8 +194,18 @@
         <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E0C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -210,11 +227,39 @@
         <color rgb="00C9C9C9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D7E0DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D7E0DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D7E0DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D7E0DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C8D2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C8D2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C8D2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C8D2CC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -353,6 +398,45 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -918,9 +1002,9 @@
           <t>clients_lines_unpivot.sql</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>UNCHANGED</t>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>RETIRE?</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -937,7 +1021,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>NOT updated yet. As written it reads `clients_report` in xvala_core, but the DDL shows the real object is `xvala_core-raw`.`pfe_clients_report`. Reference + schema correction still outstanding (also the pfe_ prefix).</t>
+          <t>Belonged to the retired vw_breach_list_cp; NOT referenced by current breach v7 or portfolio v4. Retire candidate — verify UC lineage (no downstream) before drop.</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1064,6 +1148,80 @@
       <c r="G11" s="10" t="inlineStr">
         <is>
           <t>CONFIRM it passes business_date through unfiltered — Level-1 needs every load visible for history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>vw_asts_bucket_pivot</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>—  (not in this build)</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>RETIRE?</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>(unknown — not read by current views)</t>
+        </is>
+      </c>
+      <c r="E12" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>NOT referenced by vw_asts_portfolio_cp_stress (v4) or vw_ast_breach_report (v7). No reference anywhere in the current product SQL. Retire candidate — verify UC Catalog Explorer lineage (downstream) before drop, in case another team reads it.</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>vw_asts_client_line_report</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>—  (not in this build)</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>RETIRE?</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>(unknown — not read by current views)</t>
+        </is>
+      </c>
+      <c r="E13" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>Same family as vw_clients_lines; NOT referenced by current breach v7 or portfolio v4. Breach client/line attributes come from test_ats_summary + test_lines_report instead. Retire candidate — verify UC lineage before drop.</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3633,29 +3791,169 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="40" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Modeling / Architecture</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>Duplicated logic across portfolio + breach views — no shared baseline (spine)</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>portfolio_aggregation_v4.sql AND vw_ast_breach_report_v7.sql</t>
+        </is>
+      </c>
+      <c r="E37" s="42" t="inlineStr">
+        <is>
+          <t>Both views independently re-compute the bucket-matched limit (CASE Max_Exp_Time_Bucket ladder), utilisation ratio, entity parse, rating/NIG strip. Same logic written twice -&gt; can DRIFT (one fixed, other not) -&gt; the two stop reconciling silently.</t>
+        </is>
+      </c>
+      <c r="F37" s="42" t="inlineStr">
+        <is>
+          <t>Refactor to a single LINE-GRAIN SPINE view computing this logic ONCE: every facility/line with exposure, bucket-matched limit, utilisation, breach flag, dims. Then breach = spine WHERE breach flag; portfolio = spine aggregated to counterparty. One baseline + two derivations.</t>
+        </is>
+      </c>
+      <c r="G37" s="48" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="40" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Requirements / Architecture</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>REQ: facility-counterparty view must have the SAME STRUCTURE as the breach report</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>new requirement (target design)</t>
+        </is>
+      </c>
+      <c r="E38" s="42" t="inlineStr">
+        <is>
+          <t>Facility (line) x counterparty view = breach-report column shape + grain, but UNFILTERED (all facilities, not just breaches). This makes the breach-report row shape the CANONICAL line-grain structure.</t>
+        </is>
+      </c>
+      <c r="F38" s="42" t="inlineStr">
+        <is>
+          <t>The facility-counterparty view IS the spine (n+33): line grain, breach-report structure, no breach filter. breach report = spine WHERE Excess_Breach=TRUE; portfolio = spine aggregated to counterparty. Resolves the duplication: one spine, two derivations, shared structure by construction.</t>
+        </is>
+      </c>
+      <c r="G38" s="48" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="45" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>Requirements / Conformance</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>REQ 1.1 Industry must be 5 mapped sectors (HF=SIC 7298)</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>portfolio v5 / breach v8</t>
+        </is>
+      </c>
+      <c r="E39" s="42" t="inlineStr">
+        <is>
+          <t>Portfolio cannot resolve HF (no sic_code on ats_summary); breach v8 can. Sector mapping differs between the two levels.</t>
+        </is>
+      </c>
+      <c r="F39" s="42" t="inlineStr">
+        <is>
+          <t>Portfolio best-effort text map, HF flagged. Unify by giving portfolio sic_code (join test_ats_summary or source add).</t>
+        </is>
+      </c>
+      <c r="G39" s="60" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="45" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>Requirements / Conformance</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>Display-hygiene filters (Stress&gt;0, Limit&gt;1) are NOT in the email</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="E40" s="42" t="inlineStr">
+        <is>
+          <t>Risk of drifting from rqts if treated as requirements. They are additive; the 5 email filters are the baseline.</t>
+        </is>
+      </c>
+      <c r="F40" s="42" t="inlineStr">
+        <is>
+          <t>Keep hygiene filters at dashboard layer separate from the 5 required filters. Surface excluded (limit=1) names as a count.</t>
+        </is>
+      </c>
+      <c r="G40" s="61" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Status tally:</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>Open: 6</t>
-        </is>
-      </c>
-      <c r="C38" s="36" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Open: 9</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
         <is>
           <t>Confirm: 3</t>
         </is>
       </c>
-      <c r="D38" s="31" t="inlineStr">
-        <is>
-          <t>Watch: 10</t>
-        </is>
-      </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>Watch: 11</t>
+        </is>
+      </c>
+      <c r="E42" s="29" t="inlineStr">
         <is>
           <t>Handled: 13</t>
         </is>
@@ -3668,4 +3966,612 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>Requirements Tally — Tia's email (Level 1 Portfolio / Level 2 Facility / Level 3 Line). Keep aligned: required fields+filters = baseline; out-of-box (trajectory/fingerprint) sits ON TOP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>Req #</t>
+        </is>
+      </c>
+      <c r="B2" s="54" t="inlineStr">
+        <is>
+          <t>Requirement (from email)</t>
+        </is>
+      </c>
+      <c r="C2" s="54" t="inlineStr">
+        <is>
+          <t>Where it lives</t>
+        </is>
+      </c>
+      <c r="D2" s="54" t="inlineStr">
+        <is>
+          <t>Satisfied by (view · column)</t>
+        </is>
+      </c>
+      <c r="E2" s="54" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F2" s="54" t="inlineStr">
+        <is>
+          <t>Gap / next step</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="55" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio: Stress PFE by Industry = 5 mapped sectors (HF=SIC 7298; else Financial/Banks/Government -&gt; Corporates)</t>
+        </is>
+      </c>
+      <c r="C3" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>portfolio v5 · sector</t>
+        </is>
+      </c>
+      <c r="E3" s="57" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F3" s="56" t="inlineStr">
+        <is>
+          <t>HF=7298 unresolvable from ats_summary (no sic_code). Banks/Fin/Govt/Corp mapped by text. Join test_ats_summary or add sic_code to source for exact HF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="55" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio: split OTC / SFT</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>portfolio v5 · otc_sft (page filter)</t>
+        </is>
+      </c>
+      <c r="E4" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F4" s="56" t="inlineStr">
+        <is>
+          <t>Page-by toggle on dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio: by Entity (4-digit SCREAM line code)</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>portfolio v5 · entity (parsed)</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F5" s="56" t="inlineStr">
+        <is>
+          <t>regexp first ( ) token. Wrong td_sub column avoided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio: by BRR</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>portfolio v5 · brr_bucket</t>
+        </is>
+      </c>
+      <c r="E6" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F6" s="56" t="inlineStr">
+        <is>
+          <t>NIG/leading-digit/5+ bucketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>Facility view: ALL lines at line grain, stress PFE each</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>Facility/Breach</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 (line grain) — facility = v8 minus breach filter</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F7" s="56" t="inlineStr">
+        <is>
+          <t>Breach v8 = filtered. The unfiltered facility (all lines + flag) = the SPINE, still to build (matrix rows 33/34).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>2.1.a</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>Manual: Major Risk Driver / Recurring-New / Feedback</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>Facility/Breach</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 · Major_Risk_Driver, Recurring_New, Feedback</t>
+        </is>
+      </c>
+      <c r="E8" s="57" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F8" s="56" t="inlineStr">
+        <is>
+          <t>Recurring_New real; Driver+Feedback stubs (NULL) pending ats_dshbd_breach_commentary wire-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>2.1.b</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>IM + IA columns (from SCREAM)</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>Facility/Breach</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 · IM, IA</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F9" s="56" t="inlineStr">
+        <is>
+          <t>IM=lines_report.initial_margin; IA=decomp max_usage_0_3_mo (product_group filter).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>2.1.c</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>OTC vs SFT column</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>Facility/Breach</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 · Product_Type</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F10" s="56" t="inlineStr">
+        <is>
+          <t>ats_summary.otc_sft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>2.1.d</t>
+        </is>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>Breach indicator (Y/N) on all lines</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>Facility/Portfolio</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 (implicit) ; portfolio v5 · breaches_any</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F11" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio v5 adds breaches_any so dashboard can filter-by-breaches at CP grain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>Industry = mapped sector (5 buckets) on facility</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>Facility/Breach</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 · Sector</t>
+        </is>
+      </c>
+      <c r="E12" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F12" s="56" t="inlineStr">
+        <is>
+          <t>HF=7298 resolvable here (sic_code on test_ats_summary). Granular Industry kept for display.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>Filters: breaches, industry, rating, line type, stress credit utilization</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 cols all present</t>
+        </is>
+      </c>
+      <c r="E13" s="57" t="inlineStr">
+        <is>
+          <t>TO WIRE</t>
+        </is>
+      </c>
+      <c r="F13" s="56" t="inlineStr">
+        <is>
+          <t>Build these 5 as dashboard filters on the facility/breach grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>Drill: click counterparty / line code -&gt; exposure detail</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>linked attributes + selector</t>
+        </is>
+      </c>
+      <c r="E14" s="57" t="inlineStr">
+        <is>
+          <t>TO WIRE</t>
+        </is>
+      </c>
+      <c r="F14" s="56" t="inlineStr">
+        <is>
+          <t>Level-2 -&gt; Level-3 drill (Counterparty/Line linked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>relabel</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>"Current Exposure"-&gt;Standard PFE ; "Stress Exposure"-&gt;Stress PFE</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>breach v8 · Standard_PFE_MM, Stress_PFE_MM ; portfolio · standard_pfe, stress_pfe</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F15" s="56" t="inlineStr">
+        <is>
+          <t>Naming already applied in views.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>Individual Line Tab: deals by asset class, hist max stress PFE, MTM/IM/IA, commentary</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>Line (L3)</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t>pfe_deals_report (design only)</t>
+        </is>
+      </c>
+      <c r="E16" s="59" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="F16" s="56" t="inlineStr">
+        <is>
+          <t>Level-3 tearsheet — future workstream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>Override Function: Credit Analytics corrects data, flows to all dashboards</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>write-back table (ats_dshbd_breach_commentary + override)</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="F17" s="56" t="inlineStr">
+        <is>
+          <t>Architecturally significant write-back workstream, not a column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>OOB</t>
+        </is>
+      </c>
+      <c r="B18" s="56" t="inlineStr">
+        <is>
+          <t>Out-of-box: trajectory scatter (util x stress), scenario fingerprint, MoM</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>Portfolio (on top)</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t>portfolio v5 · 8 cp_* + stress_pfe + limit_amt + utilization</t>
+        </is>
+      </c>
+      <c r="E18" s="57" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F18" s="56" t="inlineStr">
+        <is>
+          <t>Sits ON TOP of required cuts. Single-date working; MoM when history loads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>OOB</t>
+        </is>
+      </c>
+      <c r="B19" s="56" t="inlineStr">
+        <is>
+          <t>Display-hygiene filters: Stress PFE&gt;0 AND Limit Amount&gt;1</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t>Dashboard (on top)</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>dashboard layer</t>
+        </is>
+      </c>
+      <c r="E19" s="57" t="inlineStr">
+        <is>
+          <t>TO WIRE</t>
+        </is>
+      </c>
+      <c r="F19" s="56" t="inlineStr">
+        <is>
+          <t>NOT in email — additive. limit=1 = placeholder anomaly (logged).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/PFE/stress_pfe_view_matrix.xlsx
+++ b/PFE/stress_pfe_view_matrix.xlsx
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -436,6 +436,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -874,7 +886,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>portfolio_aggregation_v4.sql</t>
+          <t>portfolio_aggregation_v5.sql (v6 pending)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -884,8 +896,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ats_summary
-asts  (bucket-matched limit)</t>
+          <t>ats_summary (scenarios+dims, line grain) ; asts (bucket limit + breach flags + No_Line_Indicator). NOTE: ats_summary has NO No_Line_Indicator and NO sic_code — both must be sourced from asts / test_ats_summary.</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -896,7 +907,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>v4 (PRODUCTION-SHAPED). Now carries the FULL column set: 8 scenario sums + driver, PLUS limit_amt (asts bucket-matched, same basis as the breach view) and utilization (RATIO). History reads straight off business_date in the table (no demo). One model, demo and live. Strategy: limit_amt -&gt; Sum (now additive); utilization -&gt; do NOT Sum, use compound Sum(stress)/Sum(limit).</t>
+          <t>v5: +sector(REQ1.1, HF gap) +breaches_any(REQ2.1.d). PENDING v6: No_Line_Indicator filter via anti-join to asts (107 no-line lines confirmed leaked into ats_summary — see Join Audit); HF sic_code 7298 override; otc_leg/sft_leg split.</t>
         </is>
       </c>
       <c r="G5" s="44" t="inlineStr">
@@ -1240,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2174,147 @@
       <c r="A28" s="24" t="inlineStr">
         <is>
           <t>DEMO / TBD / moot — see Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>vw_asts_portfolio_cp_stress</t>
+        </is>
+      </c>
+      <c r="B29" s="56" t="inlineStr">
+        <is>
+          <t>ats_summary</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t>xvala_core</t>
+        </is>
+      </c>
+      <c r="E29" s="56" t="inlineStr">
+        <is>
+          <t>Read (scenario sums + dims)</t>
+        </is>
+      </c>
+      <c r="F29" s="56" t="inlineStr">
+        <is>
+          <t>line + business_date</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>Yes (GROUP BY business_date)</t>
+        </is>
+      </c>
+      <c r="H29" s="64" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="I29" s="56" t="inlineStr">
+        <is>
+          <t>DEP: line-grain source. MISSING on this table: No_Line_Indicator AND sic_code -&gt; must come from asts / test_ats_summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>vw_asts_portfolio_cp_stress</t>
+        </is>
+      </c>
+      <c r="B30" s="56" t="inlineStr">
+        <is>
+          <t>asts</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D30" s="56" t="inlineStr">
+        <is>
+          <t>xvala_core</t>
+        </is>
+      </c>
+      <c r="E30" s="56" t="inlineStr">
+        <is>
+          <t>Join (bucket limit, breach flags, No_Line_Indicator)</t>
+        </is>
+      </c>
+      <c r="F30" s="56" t="inlineStr">
+        <is>
+          <t>Line + business_date</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" s="64" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="I30" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMED: 107 no-line lines (No_Line_Indicator=TRUE) leaked into ats_summary (11,804 lines, 0 unmatched). v6 must anti-join asts to drop them — same rule as breach report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="62" t="inlineStr">
+        <is>
+          <t>vw_asts_portfolio_cp_stress</t>
+        </is>
+      </c>
+      <c r="B31" s="56" t="inlineStr">
+        <is>
+          <t>test_ats_summary</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t>xvala_core</t>
+        </is>
+      </c>
+      <c r="E31" s="56" t="inlineStr">
+        <is>
+          <t>Join (PENDING v6 — sic_code for HF=7298)</t>
+        </is>
+      </c>
+      <c r="F31" s="56" t="inlineStr">
+        <is>
+          <t>Line + business_date</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" s="64" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="I31" s="65" t="inlineStr">
+        <is>
+          <t>NEEDED: portfolio cannot resolve Hedge Funds (REQ1.1) without sic_code; ats_summary lacks it. Join test_ats_summary or have source add sic_code.</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3931,29 +4083,99 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+    <row r="41" ht="110" customHeight="1">
+      <c r="A41" s="45" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>Data Concern / Completeness</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>Limit_Amount = 1 (or 2) is a SOURCE placeholder, not a real limit</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>asts Limit_* -&gt; portfolio limit_amt, breach Limit_Amount, utilization</t>
+        </is>
+      </c>
+      <c r="E41" s="42" t="inlineStr">
+        <is>
+          <t>utilization = stress / 1 (or /2) = MILLIONS -&gt; blows up the trajectory X-axis and any compound Sum(stress)/Sum(limit). A handful of placeholder rows distort portfolio-level utilisation.</t>
+        </is>
+      </c>
+      <c r="F41" s="42" t="inlineStr">
+        <is>
+          <t>Dashboard: filter Limit Amount &gt; 1 (really &gt; a small floor, e.g. &gt;2) for display. These rows are a FINDING (exposure, no real limit) -&gt; surface as an excluded-count, not silently dropped. Root fix: source should load real limits or a documented NULL, never 1/2.</t>
+        </is>
+      </c>
+      <c r="G41" s="60" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="110" customHeight="1">
+      <c r="A42" s="45" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>Dependency / Completeness</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>Portfolio depends on ats_summary which is MISSING No_Line_Indicator + sic_code</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>vw_asts_portfolio_cp_stress &lt;- ats_summary</t>
+        </is>
+      </c>
+      <c r="E42" s="42" t="inlineStr">
+        <is>
+          <t>Two required things are not on ats_summary: (1) No_Line_Indicator (107 no-line lines confirmed leaked in) -&gt; population not clean; (2) sic_code -&gt; Hedge Funds (REQ1.1) unresolvable. Both force a join back to asts / test_ats_summary.</t>
+        </is>
+      </c>
+      <c r="F42" s="42" t="inlineStr">
+        <is>
+          <t>v6: anti-join asts on No_Line_Indicator=TRUE (drop the 107, mirror breach report); join test_ats_summary for sic_code (HF=7298). Long-term: have the ats_summary build carry No_Line_Indicator + sic_code so consumers do not re-derive.</t>
+        </is>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Status tally:</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>Open: 9</t>
-        </is>
-      </c>
-      <c r="C42" s="36" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>Open: 11</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="inlineStr">
         <is>
           <t>Confirm: 3</t>
         </is>
       </c>
-      <c r="D42" s="31" t="inlineStr">
+      <c r="D44" s="31" t="inlineStr">
         <is>
           <t>Watch: 11</t>
         </is>
       </c>
-      <c r="E42" s="29" t="inlineStr">
+      <c r="E44" s="29" t="inlineStr">
         <is>
           <t>Handled: 13</t>
         </is>

--- a/PFE/stress_pfe_view_matrix.xlsx
+++ b/PFE/stress_pfe_view_matrix.xlsx
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -448,6 +448,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2761,7 +2764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4153,31 +4156,65 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+    <row r="43" ht="120" customHeight="1">
+      <c r="A43" s="45" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>Data Hazard / Join</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>DATATYPE + FORMAT MISMATCH: asts/ats_summary store business_date as STRING yyyymmdd; test_/lines tables store it as DATE (renders yyyy-mm-dd).</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
+        <is>
+          <t>portfolio v6 + breach v7/v8/v9 joins to test_ats_summary</t>
+        </is>
+      </c>
+      <c r="E43" s="42" t="inlineStr">
+        <is>
+          <t>Joining/filtering test_ats_summary with "20260430" matched 0 rows -&gt; sic_code, sic_industry, brr, industry all NULL -&gt; Hedge Funds never appeared AND breach-report SIC/Rating coverage was silently degraded. test_lines_report already needed "2026-04-30" (was correct) so the breach view was internally inconsistent.</t>
+        </is>
+      </c>
+      <c r="F43" s="42" t="inlineStr">
+        <is>
+          <t>FIXED (datatype-agnostic): every business_date join/filter in portfolio v6 + breach v9 now uses regexp_replace(CAST(business_date AS STRING),"-","") -&gt; canonical yyyymmdd. Survives a datatype change on EITHER side (STRING-yyyymmdd / STRING-yyyy-mm-dd / DATE all normalize). RULE: never compare business_date raw across tables; always normalize. Re-validate breach SIC/Rating coverage after deploy.</t>
+        </is>
+      </c>
+      <c r="G43" s="66" t="inlineStr">
+        <is>
+          <t>Handled</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Status tally:</t>
         </is>
       </c>
-      <c r="B44" s="33" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>Open: 11</t>
         </is>
       </c>
-      <c r="C44" s="36" t="inlineStr">
+      <c r="C45" s="36" t="inlineStr">
         <is>
           <t>Confirm: 3</t>
         </is>
       </c>
-      <c r="D44" s="31" t="inlineStr">
+      <c r="D45" s="31" t="inlineStr">
         <is>
           <t>Watch: 11</t>
         </is>
       </c>
-      <c r="E44" s="29" t="inlineStr">
-        <is>
-          <t>Handled: 13</t>
+      <c r="E45" s="29" t="inlineStr">
+        <is>
+          <t>Handled: 14</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4301,17 @@
       </c>
       <c r="D3" s="56" t="inlineStr">
         <is>
-          <t>portfolio v5 · sector</t>
-        </is>
-      </c>
-      <c r="E3" s="57" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>portfolio v6 · industry (5 buckets, in place)</t>
+        </is>
+      </c>
+      <c r="E3" s="58" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="F3" s="56" t="inlineStr">
         <is>
-          <t>HF=7298 unresolvable from ats_summary (no sic_code). Banks/Fin/Govt/Corp mapped by text. Join test_ats_summary or add sic_code to source for exact HF.</t>
+          <t>FIXED: dropped dup sector; industry now 5 buckets; HF=7298 via test_ats_summary join. Dependency on test_ats_summary logged.</t>
         </is>
       </c>
     </row>

--- a/PFE/stress_pfe_view_matrix.xlsx
+++ b/PFE/stress_pfe_view_matrix.xlsx
@@ -2764,7 +2764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4191,28 +4191,64 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+    <row r="44" ht="100" customHeight="1">
+      <c r="A44" s="45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>Data Concern / Completeness</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>SIC coverage ~50% on breach set (66/132 after date-join fix)</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>test_ats_summary.sic_code / sic_industry -&gt; breach Sector, portfolio HF map</t>
+        </is>
+      </c>
+      <c r="E44" s="42" t="inlineStr">
+        <is>
+          <t>Join is now correct (66/132, up from 60; Hedge Funds confirmed present). Remaining ~half of breached lines have NULL sic_code -&gt; they fall to the ELSE branch = Corporates, even if truly Banks/Govt/HF. Sector accuracy is BOUNDED by source SIC coverage, not by the view.</t>
+        </is>
+      </c>
+      <c r="F44" s="42" t="inlineStr">
+        <is>
+          <t>Not a view bug — source completeness. Flag to business: fuller sic_code population on test_ats_summary (or the clients source) needed for complete sector/HF classification. View already maps everything available; nulls -&gt; Corporates by design.</t>
+        </is>
+      </c>
+      <c r="G44" s="61" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Status tally:</t>
         </is>
       </c>
-      <c r="B45" s="33" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>Open: 11</t>
         </is>
       </c>
-      <c r="C45" s="36" t="inlineStr">
+      <c r="C46" s="36" t="inlineStr">
         <is>
           <t>Confirm: 3</t>
         </is>
       </c>
-      <c r="D45" s="31" t="inlineStr">
-        <is>
-          <t>Watch: 11</t>
-        </is>
-      </c>
-      <c r="E45" s="29" t="inlineStr">
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>Watch: 12</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="inlineStr">
         <is>
           <t>Handled: 14</t>
         </is>

--- a/PFE/stress_pfe_view_matrix.xlsx
+++ b/PFE/stress_pfe_view_matrix.xlsx
@@ -818,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1236,6 +1236,80 @@
       <c r="G13" s="51" t="inlineStr">
         <is>
           <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line.sql</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>NEW (L3)</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>pfe_deals_report (xvala_core-raw)</t>
+        </is>
+      </c>
+      <c r="E14" s="63" t="inlineStr">
+        <is>
+          <t>core-raw</t>
+        </is>
+      </c>
+      <c r="F14" s="56" t="inlineStr">
+        <is>
+          <t>Level-3 deal-grain view: deals under a line, asset class (deal_type), MTM, notional, override. Drill key = line.</t>
+        </is>
+      </c>
+      <c r="G14" s="56" t="inlineStr">
+        <is>
+          <t>business_date yyyymmdd (string); normalized pattern applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_assetclass_summary</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_assetclass_summary.sql</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>NEW (L3)</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="inlineStr">
+        <is>
+          <t>core-raw</t>
+        </is>
+      </c>
+      <c r="F15" s="56" t="inlineStr">
+        <is>
+          <t>Asset-class summary: line x asset_class, deal_count + SUM(MTM USD). Notional NOT summed (multi-ccy).</t>
+        </is>
+      </c>
+      <c r="G15" s="56" t="inlineStr">
+        <is>
+          <t>inherits</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -2318,6 +2392,100 @@
       <c r="I31" s="65" t="inlineStr">
         <is>
           <t>NEEDED: portfolio cannot resolve Hedge Funds (REQ1.1) without sic_code; ats_summary lacks it. Join test_ats_summary or have source add sic_code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="62" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line</t>
+        </is>
+      </c>
+      <c r="B32" s="56" t="inlineStr">
+        <is>
+          <t>pfe_deals_report</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t>xvala_core-raw</t>
+        </is>
+      </c>
+      <c r="E32" s="56" t="inlineStr">
+        <is>
+          <t>Read (deal grain)</t>
+        </is>
+      </c>
+      <c r="F32" s="56" t="inlineStr">
+        <is>
+          <t>line (drill key); business_date</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>Yes (no_line filter; per-date)</t>
+        </is>
+      </c>
+      <c r="H32" s="64" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="I32" s="65" t="inlineStr">
+        <is>
+          <t>DEP: deal grain. Money cols STRING -&gt; CAST DOUBLE. business_date yyyymmdd string. NO deal-level stress PFE (only deal_m2m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_assetclass_summary</t>
+        </is>
+      </c>
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="inlineStr">
+        <is>
+          <t>xvala_core-raw</t>
+        </is>
+      </c>
+      <c r="E33" s="56" t="inlineStr">
+        <is>
+          <t>Aggregate (line x asset_class)</t>
+        </is>
+      </c>
+      <c r="F33" s="56" t="inlineStr">
+        <is>
+          <t>line, asset_class, business_date</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" s="64" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="I33" s="65" t="inlineStr">
+        <is>
+          <t>MTM summed (USD). Notional NOT summed (multi-currency).</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4226,29 +4394,99 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+    <row r="45" ht="96" customHeight="1">
+      <c r="A45" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>Data Concern / Additivity</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
+        <is>
+          <t>Deal notional (principal_1/2) is MULTI-CURRENCY -&gt; NOT additive</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line -&gt; assetclass summary</t>
+        </is>
+      </c>
+      <c r="E45" s="42" t="inlineStr">
+        <is>
+          <t>principal_1 currency varies (USD/JPY/CLP/EUR/HUF...). Summing across deals is meaningless without FX conversion. deal_m2m is USD (additive).</t>
+        </is>
+      </c>
+      <c r="F45" s="42" t="inlineStr">
+        <is>
+          <t>Summary view sums MTM (USD) + deal COUNT only; notional kept per-deal, not summed. To sum notional, convert to USD via an FX rate (not available air-gapped) or filter to one currency.</t>
+        </is>
+      </c>
+      <c r="G45" s="61" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="96" customHeight="1">
+      <c r="A46" s="45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>Requirements / Coverage</t>
+        </is>
+      </c>
+      <c r="C46" s="42" t="inlineStr">
+        <is>
+          <t>pfe_deals_report has NO deal-level stress PFE</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr">
+        <is>
+          <t>Level-3 line tab</t>
+        </is>
+      </c>
+      <c r="E46" s="42" t="inlineStr">
+        <is>
+          <t>Email asks Level-3 deals + historical max stress PFE. Deal table has only deal_m2m (MTM), no per-deal PFE. Stress PFE is a LINE total (asts).</t>
+        </is>
+      </c>
+      <c r="F46" s="42" t="inlineStr">
+        <is>
+          <t>Level-3 deal breakdown shows MTM + count by asset class; the historical stress-PFE trend sources asts/portfolio at LINE grain, not deals. Confirm acceptable with business.</t>
+        </is>
+      </c>
+      <c r="G46" s="60" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Status tally:</t>
         </is>
       </c>
-      <c r="B46" s="33" t="inlineStr">
-        <is>
-          <t>Open: 11</t>
-        </is>
-      </c>
-      <c r="C46" s="36" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>Open: 12</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="inlineStr">
         <is>
           <t>Confirm: 3</t>
         </is>
       </c>
-      <c r="D46" s="31" t="inlineStr">
-        <is>
-          <t>Watch: 12</t>
-        </is>
-      </c>
-      <c r="E46" s="29" t="inlineStr">
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>Watch: 13</t>
+        </is>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
         <is>
           <t>Handled: 14</t>
         </is>
@@ -4753,17 +4991,17 @@
       </c>
       <c r="D16" s="56" t="inlineStr">
         <is>
-          <t>pfe_deals_report (design only)</t>
-        </is>
-      </c>
-      <c r="E16" s="59" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
+          <t>vw_pfe_deals_by_line + vw_pfe_deals_assetclass_summary</t>
+        </is>
+      </c>
+      <c r="E16" s="57" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F16" s="56" t="inlineStr">
         <is>
-          <t>Level-3 tearsheet — future workstream.</t>
+          <t>Deal view + asset-class summary built (deal_type=asset class, MTM/count). GAPS: no deal-level stress PFE (line-level only); notional multi-ccy not summable. Historical stress-PFE trend sources asts at line grain.</t>
         </is>
       </c>
     </row>

--- a/PFE/stress_pfe_view_matrix.xlsx
+++ b/PFE/stress_pfe_view_matrix.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base Tables" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Anomalies &amp; Conformance" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements Tally" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grain Reference" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'View Matrix'!$A$4:$G$11</definedName>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,8 +92,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -204,6 +211,16 @@
         <fgColor rgb="001F4E5F"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8E4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -259,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -453,6 +470,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2932,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4464,31 +4491,135 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+    <row r="47" ht="92" customHeight="1">
+      <c r="A47" s="45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t>Grain / Key</t>
+        </is>
+      </c>
+      <c r="C47" s="42" t="inlineStr">
+        <is>
+          <t>pfe_deals_report grain = deal_id x LINE (not deal_id alone)</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line + any deal join</t>
+        </is>
+      </c>
+      <c r="E47" s="42" t="inlineStr">
+        <is>
+          <t>Confirmed: same deal_id appears on multiple lines (e.g. 1656448 on CITI and SHQ). deal_id is NOT unique on its own. Deal joins/counts must key on deal_id + line. Count Distinct(Deal) counts a multi-line deal once globally, once per line locally.</t>
+        </is>
+      </c>
+      <c r="F47" s="42" t="inlineStr">
+        <is>
+          <t>Document grain in product spec. Any deal-level join uses deal_id+line. Strategy Deal attribute keyed deal_id+line if global uniqueness needed.</t>
+        </is>
+      </c>
+      <c r="G47" s="67" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="92" customHeight="1">
+      <c r="A48" s="45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t>Calc / Precision</t>
+        </is>
+      </c>
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>ROUND() on a stored fraction summed across 100k+ rows destroyed the total</t>
+        </is>
+      </c>
+      <c r="D48" s="42" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line MTM_Share_Of_Line</t>
+        </is>
+      </c>
+      <c r="E48" s="42" t="inlineStr">
+        <is>
+          <t>LCH1 has 218,737 deals; each share ~1e-6. ROUND(share,4) floored most to 0 -&gt; shares summed to 0.607 not 1.0. Window/join/dates all verified correct; rounding was the bug.</t>
+        </is>
+      </c>
+      <c r="F48" s="42" t="inlineStr">
+        <is>
+          <t>FIXED: store shares at FULL precision, no ROUND. Round at DISPLAY only (Strategy formatting). RULE: never round a value that is later summed across many rows.</t>
+        </is>
+      </c>
+      <c r="G48" s="66" t="inlineStr">
+        <is>
+          <t>Handled</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="92" customHeight="1">
+      <c r="A49" s="45" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t>Date / Output Format</t>
+        </is>
+      </c>
+      <c r="C49" s="42" t="inlineStr">
+        <is>
+          <t>Views emitted raw business_date (mixed string yyyymmdd / yyyy-mm-dd / DATE)</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>deal view, spine, portfolio v6</t>
+        </is>
+      </c>
+      <c r="E49" s="42" t="inlineStr">
+        <is>
+          <t>Comparisons were datatype-agnostic but OUTPUT date passed through source format inconsistently. User req: consistent date on output regardless of source datatype.</t>
+        </is>
+      </c>
+      <c r="F49" s="42" t="inlineStr">
+        <is>
+          <t>FIXED: every view emits to_date(regexp_replace(CAST(business_date AS STRING),"-",""),"yyyyMMdd") -&gt; a real DATE. Survives any source datatype change. Breach v9 emits no date (internal only).</t>
+        </is>
+      </c>
+      <c r="G49" s="66" t="inlineStr">
+        <is>
+          <t>Handled</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>Status tally:</t>
         </is>
       </c>
-      <c r="B48" s="33" t="inlineStr">
+      <c r="B51" s="33" t="inlineStr">
         <is>
           <t>Open: 12</t>
         </is>
       </c>
-      <c r="C48" s="36" t="inlineStr">
-        <is>
-          <t>Confirm: 3</t>
-        </is>
-      </c>
-      <c r="D48" s="31" t="inlineStr">
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>Confirm: 4</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
         <is>
           <t>Watch: 13</t>
         </is>
       </c>
-      <c r="E48" s="29" t="inlineStr">
-        <is>
-          <t>Handled: 14</t>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t>Handled: 16</t>
         </is>
       </c>
     </row>
@@ -5107,4 +5238,194 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>View / Object</t>
+        </is>
+      </c>
+      <c r="B1" s="68" t="inlineStr">
+        <is>
+          <t>Grain (one row per...)</t>
+        </is>
+      </c>
+      <c r="C1" s="68" t="inlineStr">
+        <is>
+          <t>Key columns</t>
+        </is>
+      </c>
+      <c r="D1" s="68" t="inlineStr">
+        <is>
+          <t>Additivity notes</t>
+        </is>
+      </c>
+      <c r="E1" s="68" t="inlineStr">
+        <is>
+          <t>Date output</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>vw_asts_portfolio_cp_stress (portfolio v6)</t>
+        </is>
+      </c>
+      <c r="B2" s="69" t="inlineStr">
+        <is>
+          <t>counterparty x otc_sft x entity x business_date</t>
+        </is>
+      </c>
+      <c r="C2" s="42" t="inlineStr">
+        <is>
+          <t>counterparty, otc_sft, entity, business_date</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
+        <is>
+          <t>stress_pfe / 8 scenarios / limit_amt = SUM (additive). utilization = RATIO (non-additive, divide at display).</t>
+        </is>
+      </c>
+      <c r="E2" s="42" t="inlineStr">
+        <is>
+          <t>DATE (normalized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" s="45" t="inlineStr">
+        <is>
+          <t>vw_ast_breach_report (breach v9)</t>
+        </is>
+      </c>
+      <c r="B3" s="69" t="inlineStr">
+        <is>
+          <t>line (breached lines only) x business_date</t>
+        </is>
+      </c>
+      <c r="C3" s="42" t="inlineStr">
+        <is>
+          <t>Line, business_date (internal)</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
+        <is>
+          <t>MTM/Stress/Standard PFE/IM/IA = SUM. Stress_Credit_Utilization = RATIO. Limit_Amount = SUM (denominator).</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
+        <is>
+          <t>none (single-load snapshot, internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>vw_line_stress_spine</t>
+        </is>
+      </c>
+      <c r="B4" s="69" t="inlineStr">
+        <is>
+          <t>line x business_date (ALL lines)</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>Line, business_date</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>Stress_PFE/Limit = per line. Utilization = RATIO. Breach_Status/Worst_Scenario = line attributes.</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
+        <is>
+          <t>DATE (normalized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="67" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_by_line</t>
+        </is>
+      </c>
+      <c r="B5" s="69" t="inlineStr">
+        <is>
+          <t>deal_id x LINE x business_date</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>deal_id + line (deal_id NOT unique alone!)</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>MTM (deal_m2m USD) = SUM. Notional = MULTI-CCY, NOT summable. MTM_Share_Of_Line = fraction (full precision, sums to 1 per line). Line_* breach cols = line attributes repeated on deals, do NOT sum.</t>
+        </is>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
+          <t>DATE (normalized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>vw_pfe_deals_assetclass_summary</t>
+        </is>
+      </c>
+      <c r="B6" s="69" t="inlineStr">
+        <is>
+          <t>line x asset_class x business_date</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>line, asset_class, business_date</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>Deal_Count = COUNT. MTM_USD = SUM. Notional NOT summed.</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>inherits deal view</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>KEY GRAIN FINDING: pfe_deals_report is deal_id x LINE — a single deal can be booked on multiple credit lines. Joins and uniqueness must use deal_id + line together.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>